--- a/excel_data/gcg_cardlist_promo.xlsx
+++ b/excel_data/gcg_cardlist_promo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FLC\Desktop\JavaScript\Gundam Card Web\gundam-card-web\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05776291-E0A9-4F20-B592-301946BA0F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012206F8-2254-4126-957E-411D8A977B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="3810" windowWidth="21780" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2950" yWindow="2890" windowWidth="20090" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="推廣卡_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="410">
   <si>
     <t>序號</t>
   </si>
@@ -1265,12 +1265,95 @@
     <t>官方遊戲墊板&amp;卡牌套裝 蘇萊塔＆米奧琳涅 [EVX02]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>出自作品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機動戦士ガンダム</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダム 水星の魔女</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダムSEED</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダムUC</t>
+  </si>
+  <si>
+    <t>新機動戦記ガンダムW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機動戦士ガンダム 鉄血のオルフェンズ</t>
+  </si>
+  <si>
+    <t>機動戦士Gundam GQuuuuuuX(ジークアクス)</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダム00</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダム 閃光のハサウェイ</t>
+  </si>
+  <si>
+    <t>機動戦士Zガンダム</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダムAGE</t>
+  </si>
+  <si>
+    <t>機動新世紀ガンダムX</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダム0080 ポケットの中の戦争</t>
+  </si>
+  <si>
+    <t>機動戦士ガンダムSEED DESTINY</t>
+  </si>
+  <si>
+    <t>機動戦士Vガンダム</t>
+  </si>
+  <si>
+    <t>機動武闘伝Gガンダム</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>∀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ガンダム</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDガンダム ジージェネレーション エターナル</t>
+  </si>
+  <si>
+    <t>その他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1299,6 +1382,18 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1320,8 +1415,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1624,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
@@ -1632,7 +1728,7 @@
     <col min="5" max="5" width="60.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1648,8 +1744,11 @@
       <c r="E1" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1665,8 +1764,11 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1682,8 +1784,11 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1699,8 +1804,11 @@
       <c r="E4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1716,8 +1824,11 @@
       <c r="E5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1733,8 +1844,11 @@
       <c r="E6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1750,8 +1864,11 @@
       <c r="E7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1767,8 +1884,11 @@
       <c r="E8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1784,8 +1904,11 @@
       <c r="E9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1801,8 +1924,11 @@
       <c r="E10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1818,8 +1944,11 @@
       <c r="E11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1835,8 +1964,11 @@
       <c r="E12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1852,8 +1984,11 @@
       <c r="E13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1869,8 +2004,11 @@
       <c r="E14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -1886,8 +2024,11 @@
       <c r="E15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1903,8 +2044,11 @@
       <c r="E16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1920,8 +2064,11 @@
       <c r="E17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1937,8 +2084,11 @@
       <c r="E18" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1954,8 +2104,11 @@
       <c r="E19" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1971,8 +2124,11 @@
       <c r="E20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1988,8 +2144,11 @@
       <c r="E21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -2005,8 +2164,11 @@
       <c r="E22" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -2022,8 +2184,11 @@
       <c r="E23" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2039,8 +2204,11 @@
       <c r="E24" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2056,8 +2224,11 @@
       <c r="E25" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2073,8 +2244,11 @@
       <c r="E26" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -2090,8 +2264,11 @@
       <c r="E27" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -2107,8 +2284,11 @@
       <c r="E28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -2124,8 +2304,11 @@
       <c r="E29" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -2141,8 +2324,11 @@
       <c r="E30" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -2158,8 +2344,11 @@
       <c r="E31" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -2175,8 +2364,11 @@
       <c r="E32" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -2192,8 +2384,11 @@
       <c r="E33" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2209,8 +2404,11 @@
       <c r="E34" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -2226,8 +2424,11 @@
       <c r="E35" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -2243,8 +2444,11 @@
       <c r="E36" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -2260,8 +2464,11 @@
       <c r="E37" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -2277,8 +2484,11 @@
       <c r="E38" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -2294,8 +2504,11 @@
       <c r="E39" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -2311,8 +2524,11 @@
       <c r="E40" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -2328,8 +2544,11 @@
       <c r="E41" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>102</v>
       </c>
@@ -2345,8 +2564,11 @@
       <c r="E42" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>103</v>
       </c>
@@ -2362,8 +2584,11 @@
       <c r="E43" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>106</v>
       </c>
@@ -2379,8 +2604,11 @@
       <c r="E44" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>108</v>
       </c>
@@ -2396,8 +2624,11 @@
       <c r="E45" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>111</v>
       </c>
@@ -2413,8 +2644,11 @@
       <c r="E46" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>114</v>
       </c>
@@ -2430,8 +2664,11 @@
       <c r="E47" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -2447,8 +2684,11 @@
       <c r="E48" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>119</v>
       </c>
@@ -2464,8 +2704,11 @@
       <c r="E49" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>121</v>
       </c>
@@ -2481,8 +2724,11 @@
       <c r="E50" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>122</v>
       </c>
@@ -2498,8 +2744,11 @@
       <c r="E51" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>125</v>
       </c>
@@ -2515,8 +2764,11 @@
       <c r="E52" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -2532,8 +2784,11 @@
       <c r="E53" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>130</v>
       </c>
@@ -2549,8 +2804,11 @@
       <c r="E54" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>132</v>
       </c>
@@ -2566,8 +2824,11 @@
       <c r="E55" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>135</v>
       </c>
@@ -2583,8 +2844,11 @@
       <c r="E56" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -2600,8 +2864,11 @@
       <c r="E57" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>140</v>
       </c>
@@ -2617,8 +2884,11 @@
       <c r="E58" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>142</v>
       </c>
@@ -2634,8 +2904,11 @@
       <c r="E59" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>144</v>
       </c>
@@ -2651,8 +2924,11 @@
       <c r="E60" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>146</v>
       </c>
@@ -2668,8 +2944,11 @@
       <c r="E61" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>147</v>
       </c>
@@ -2685,8 +2964,11 @@
       <c r="E62" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>149</v>
       </c>
@@ -2702,8 +2984,11 @@
       <c r="E63" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>151</v>
       </c>
@@ -2719,8 +3004,11 @@
       <c r="E64" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>152</v>
       </c>
@@ -2736,8 +3024,11 @@
       <c r="E65" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>154</v>
       </c>
@@ -2753,8 +3044,11 @@
       <c r="E66" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>156</v>
       </c>
@@ -2770,8 +3064,11 @@
       <c r="E67" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -2787,8 +3084,11 @@
       <c r="E68" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>161</v>
       </c>
@@ -2804,8 +3104,11 @@
       <c r="E69" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F69" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -2821,8 +3124,11 @@
       <c r="E70" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F70" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>164</v>
       </c>
@@ -2838,8 +3144,11 @@
       <c r="E71" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F71" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>165</v>
       </c>
@@ -2855,8 +3164,11 @@
       <c r="E72" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F72" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>167</v>
       </c>
@@ -2872,8 +3184,11 @@
       <c r="E73" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F73" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -2889,8 +3204,11 @@
       <c r="E74" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>170</v>
       </c>
@@ -2906,8 +3224,11 @@
       <c r="E75" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F75" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>173</v>
       </c>
@@ -2923,8 +3244,11 @@
       <c r="E76" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>175</v>
       </c>
@@ -2940,8 +3264,11 @@
       <c r="E77" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>176</v>
       </c>
@@ -2957,8 +3284,11 @@
       <c r="E78" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F78" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>178</v>
       </c>
@@ -2974,8 +3304,11 @@
       <c r="E79" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F79" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>179</v>
       </c>
@@ -2991,8 +3324,11 @@
       <c r="E80" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F80" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>181</v>
       </c>
@@ -3008,8 +3344,11 @@
       <c r="E81" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F81" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>182</v>
       </c>
@@ -3025,8 +3364,11 @@
       <c r="E82" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F82" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>185</v>
       </c>
@@ -3042,8 +3384,11 @@
       <c r="E83" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>188</v>
       </c>
@@ -3059,8 +3404,11 @@
       <c r="E84" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F84" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>190</v>
       </c>
@@ -3076,8 +3424,11 @@
       <c r="E85" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F85" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>192</v>
       </c>
@@ -3093,8 +3444,11 @@
       <c r="E86" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F86" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>193</v>
       </c>
@@ -3110,8 +3464,11 @@
       <c r="E87" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F87" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>195</v>
       </c>
@@ -3127,8 +3484,11 @@
       <c r="E88" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F88" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -3144,8 +3504,11 @@
       <c r="E89" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F89" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -3161,8 +3524,11 @@
       <c r="E90" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F90" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>199</v>
       </c>
@@ -3178,8 +3544,11 @@
       <c r="E91" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F91" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -3195,8 +3564,11 @@
       <c r="E92" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F92" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>203</v>
       </c>
@@ -3212,8 +3584,11 @@
       <c r="E93" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F93" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>204</v>
       </c>
@@ -3229,8 +3604,11 @@
       <c r="E94" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F94" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>206</v>
       </c>
@@ -3246,8 +3624,11 @@
       <c r="E95" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F95" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>207</v>
       </c>
@@ -3263,8 +3644,11 @@
       <c r="E96" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F96" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>209</v>
       </c>
@@ -3280,8 +3664,11 @@
       <c r="E97" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F97" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>210</v>
       </c>
@@ -3297,8 +3684,11 @@
       <c r="E98" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F98" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>212</v>
       </c>
@@ -3314,8 +3704,11 @@
       <c r="E99" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F99" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>214</v>
       </c>
@@ -3331,8 +3724,11 @@
       <c r="E100" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F100" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>215</v>
       </c>
@@ -3348,8 +3744,11 @@
       <c r="E101" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F101" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>217</v>
       </c>
@@ -3365,8 +3764,11 @@
       <c r="E102" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F102" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>219</v>
       </c>
@@ -3382,8 +3784,11 @@
       <c r="E103" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F103" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>220</v>
       </c>
@@ -3399,8 +3804,11 @@
       <c r="E104" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F104" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>223</v>
       </c>
@@ -3416,8 +3824,11 @@
       <c r="E105" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F105" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -3433,8 +3844,11 @@
       <c r="E106" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F106" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3450,8 +3864,11 @@
       <c r="E107" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F107" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>228</v>
       </c>
@@ -3467,8 +3884,11 @@
       <c r="E108" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F108" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>231</v>
       </c>
@@ -3484,8 +3904,11 @@
       <c r="E109" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F109" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>234</v>
       </c>
@@ -3501,8 +3924,11 @@
       <c r="E110" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F110" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>236</v>
       </c>
@@ -3518,8 +3944,11 @@
       <c r="E111" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F111" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>238</v>
       </c>
@@ -3535,8 +3964,11 @@
       <c r="E112" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F112" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>239</v>
       </c>
@@ -3552,8 +3984,11 @@
       <c r="E113" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F113" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -3569,8 +4004,11 @@
       <c r="E114" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F114" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>244</v>
       </c>
@@ -3586,8 +4024,11 @@
       <c r="E115" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F115" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>245</v>
       </c>
@@ -3603,8 +4044,11 @@
       <c r="E116" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F116" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>247</v>
       </c>
@@ -3620,8 +4064,11 @@
       <c r="E117" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F117" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>248</v>
       </c>
@@ -3637,8 +4084,11 @@
       <c r="E118" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F118" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>250</v>
       </c>
@@ -3654,8 +4104,11 @@
       <c r="E119" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F119" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -3671,8 +4124,11 @@
       <c r="E120" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F120" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>253</v>
       </c>
@@ -3688,8 +4144,11 @@
       <c r="E121" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F121" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>255</v>
       </c>
@@ -3705,8 +4164,11 @@
       <c r="E122" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F122" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>257</v>
       </c>
@@ -3722,8 +4184,11 @@
       <c r="E123" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F123" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>259</v>
       </c>
@@ -3739,8 +4204,11 @@
       <c r="E124" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F124" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>260</v>
       </c>
@@ -3756,8 +4224,11 @@
       <c r="E125" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F125" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>262</v>
       </c>
@@ -3773,8 +4244,11 @@
       <c r="E126" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F126" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>264</v>
       </c>
@@ -3790,8 +4264,11 @@
       <c r="E127" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F127" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>265</v>
       </c>
@@ -3807,8 +4284,11 @@
       <c r="E128" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F128" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -3824,8 +4304,11 @@
       <c r="E129" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F129" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>270</v>
       </c>
@@ -3841,8 +4324,11 @@
       <c r="E130" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F130" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>272</v>
       </c>
@@ -3858,8 +4344,11 @@
       <c r="E131" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="F131" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>275</v>
       </c>
@@ -3875,8 +4364,11 @@
       <c r="E132" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F132" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>278</v>
       </c>
@@ -3892,8 +4384,11 @@
       <c r="E133" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F133" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>281</v>
       </c>
@@ -3909,8 +4404,11 @@
       <c r="E134" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F134" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>284</v>
       </c>
@@ -3926,8 +4424,11 @@
       <c r="E135" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F135" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>286</v>
       </c>
@@ -3943,8 +4444,11 @@
       <c r="E136" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F136" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>288</v>
       </c>
@@ -3960,8 +4464,11 @@
       <c r="E137" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="F137" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>290</v>
       </c>
@@ -3977,8 +4484,11 @@
       <c r="E138" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F138" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>292</v>
       </c>
@@ -3994,8 +4504,11 @@
       <c r="E139" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F139" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>294</v>
       </c>
@@ -4011,8 +4524,11 @@
       <c r="E140" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F140" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>297</v>
       </c>
@@ -4028,8 +4544,11 @@
       <c r="E141" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F141" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>300</v>
       </c>
@@ -4045,8 +4564,11 @@
       <c r="E142" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F142" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>302</v>
       </c>
@@ -4062,8 +4584,11 @@
       <c r="E143" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F143" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>304</v>
       </c>
@@ -4079,8 +4604,11 @@
       <c r="E144" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F144" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>306</v>
       </c>
@@ -4096,8 +4624,11 @@
       <c r="E145" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F145" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>308</v>
       </c>
@@ -4113,8 +4644,11 @@
       <c r="E146" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F146" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>310</v>
       </c>
@@ -4130,8 +4664,11 @@
       <c r="E147" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F147" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>312</v>
       </c>
@@ -4147,8 +4684,11 @@
       <c r="E148" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F148" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>314</v>
       </c>
@@ -4164,8 +4704,11 @@
       <c r="E149" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F149" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>316</v>
       </c>
@@ -4181,8 +4724,11 @@
       <c r="E150" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F150" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>318</v>
       </c>
@@ -4198,8 +4744,11 @@
       <c r="E151" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F151" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>320</v>
       </c>
@@ -4215,8 +4764,11 @@
       <c r="E152" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F152" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>322</v>
       </c>
@@ -4232,8 +4784,11 @@
       <c r="E153" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F153" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>324</v>
       </c>
@@ -4249,8 +4804,11 @@
       <c r="E154" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F154" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>327</v>
       </c>
@@ -4266,8 +4824,11 @@
       <c r="E155" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F155" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>330</v>
       </c>
@@ -4283,8 +4844,11 @@
       <c r="E156" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F156" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>332</v>
       </c>
@@ -4300,8 +4864,11 @@
       <c r="E157" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F157" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>334</v>
       </c>
@@ -4317,8 +4884,11 @@
       <c r="E158" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F158" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="85.5" x14ac:dyDescent="5.0999999999999996">
       <c r="A159" t="s">
         <v>336</v>
       </c>
@@ -4334,8 +4904,11 @@
       <c r="E159" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F159" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>338</v>
       </c>
@@ -4351,8 +4924,11 @@
       <c r="E160" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F160" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>340</v>
       </c>
@@ -4368,8 +4944,11 @@
       <c r="E161" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F161" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>342</v>
       </c>
@@ -4385,8 +4964,11 @@
       <c r="E162" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F162" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>344</v>
       </c>
@@ -4402,8 +4984,11 @@
       <c r="E163" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="F163" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>346</v>
       </c>
@@ -4419,8 +5004,11 @@
       <c r="E164" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F164" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>349</v>
       </c>
@@ -4436,8 +5024,11 @@
       <c r="E165" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F165" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>352</v>
       </c>
@@ -4453,8 +5044,11 @@
       <c r="E166" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F166" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>355</v>
       </c>
@@ -4470,8 +5064,11 @@
       <c r="E167" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F167" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>358</v>
       </c>
@@ -4487,8 +5084,11 @@
       <c r="E168" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F168" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>361</v>
       </c>
@@ -4504,8 +5104,11 @@
       <c r="E169" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F169" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>364</v>
       </c>
@@ -4521,8 +5124,11 @@
       <c r="E170" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F170" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>366</v>
       </c>
@@ -4538,8 +5144,11 @@
       <c r="E171" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F171" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>368</v>
       </c>
@@ -4555,8 +5164,11 @@
       <c r="E172" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F172" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>370</v>
       </c>
@@ -4572,8 +5184,11 @@
       <c r="E173" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F173" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>372</v>
       </c>
@@ -4589,8 +5204,11 @@
       <c r="E174" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F174" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>374</v>
       </c>
@@ -4606,8 +5224,11 @@
       <c r="E175" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F175" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>376</v>
       </c>
@@ -4623,8 +5244,11 @@
       <c r="E176" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F176" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>379</v>
       </c>
@@ -4640,8 +5264,11 @@
       <c r="E177" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F177" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>381</v>
       </c>
@@ -4656,6 +5283,9 @@
       </c>
       <c r="E178" t="s">
         <v>389</v>
+      </c>
+      <c r="F178" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/excel_data/gcg_cardlist_promo.xlsx
+++ b/excel_data/gcg_cardlist_promo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FLC\Desktop\JavaScript\Gundam Card Web\gundam-card-web\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012206F8-2254-4126-957E-411D8A977B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48335F6F-C087-4EEE-8A56-1BC0614AE73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2950" yWindow="2890" windowWidth="20090" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17700" yWindow="2640" windowWidth="20380" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="推廣卡_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="502">
   <si>
     <t>序號</t>
   </si>
@@ -1346,6 +1346,309 @@
   </si>
   <si>
     <t>その他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>入手情報 [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>JP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROMO178</t>
+  </si>
+  <si>
+    <t>PROMO179</t>
+  </si>
+  <si>
+    <t>PROMO180</t>
+  </si>
+  <si>
+    <t>GD05-042</t>
+  </si>
+  <si>
+    <t>GD05-120</t>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXBP-018</t>
+  </si>
+  <si>
+    <t>P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機動武闘伝Gガンダム</t>
+  </si>
+  <si>
+    <t>新弾限定戦[GD05] 参加記念品</t>
+  </si>
+  <si>
+    <t>『機動戦士ガンダム 閃光のハサウェイ キルケーの魔女』3週目入場者プレゼント</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 25-26 JAPAN FINAL 3位記念品</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 25-26 JAPAN FINAL 2位記念品</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 25-26 JAPAN FINAL 優勝記念品</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 25-26 JAPAN FINAL 参加記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION1上位入賞記念品</t>
+  </si>
+  <si>
+    <t>ショップバトル 2025　SEASON1 参加者パック01</t>
+  </si>
+  <si>
+    <t>ショップバトル 2025　SEASON1 優勝者パック01</t>
+  </si>
+  <si>
+    <t>GCG EXPO来場記念品</t>
+  </si>
+  <si>
+    <t>チャンピオンシップ上位賞カード01</t>
+  </si>
+  <si>
+    <t>チャンピオンシップ 参加賞パック 01</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 25-26 GRAND FINAL 参加記念品</t>
+  </si>
+  <si>
+    <t>スタートデッキリリースイベント[ST01-ST04] リンクユニットセット</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION1 上位入賞記念品</t>
+  </si>
+  <si>
+    <t>ショップバトル2026 SEASON2　参加者パック</t>
+  </si>
+  <si>
+    <t>ショップバトル2026 SEASON2　優勝者パック</t>
+  </si>
+  <si>
+    <t>スタートデッキリリースイベント[ST05]</t>
+  </si>
+  <si>
+    <t>Vジャンプ 12月特大号 付録カード</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION 3 参加記念品</t>
+  </si>
+  <si>
+    <t>10枚まで入れ替えOK！スタートデッキカスタムバトル！</t>
+  </si>
+  <si>
+    <t>ビギナーズバトル2025 SEASON2 参加記念品</t>
+  </si>
+  <si>
+    <t>WORLD CHAPIONSHIPS 26-27 店舗予選　優勝記念品</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 26-27 Season 1上位入賞記念品</t>
+  </si>
+  <si>
+    <t>ショップバトル2025 SEASON2　参加者パック</t>
+  </si>
+  <si>
+    <t>ショップバトル2025 SEASON2　優勝者パック</t>
+  </si>
+  <si>
+    <t>スタートデッキそのままバトル！[ST07][ST08]</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION2 優勝記念品</t>
+  </si>
+  <si>
+    <t>ショップバトル 2026 SEASON1 参加者パック03</t>
+  </si>
+  <si>
+    <t>ショップバトル 2026 SEASON1 優勝者パック03</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION2 上位入賞記念品</t>
+  </si>
+  <si>
+    <t>ブースターパックリリースイベント[GD01] リンクユニットセット</t>
+  </si>
+  <si>
+    <t>ビギナーズバトル 2025 SEASON1参加記念品</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 26-27 参加賞パック Vol.1</t>
+  </si>
+  <si>
+    <t>チャンピオンシップ優勝賞カード01</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION1 優勝記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION1優勝記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION1参加記念品</t>
+  </si>
+  <si>
+    <t>ブースターパックリリースイベント[GD02]</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION3 優勝記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION 3 上位入賞記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION2</t>
+  </si>
+  <si>
+    <t>ガンダムエース 1月号 付録カード</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION3 上位入賞記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2025 MISSION3 参加記念品</t>
+  </si>
+  <si>
+    <t>ショップバトル 2026 SEASON1参加者パック03</t>
+  </si>
+  <si>
+    <t>ショップバトル 2026 SEASON 優勝者パック03</t>
+  </si>
+  <si>
+    <t>新弾限定戦[ST07][ST08][GD03]</t>
+  </si>
+  <si>
+    <t>WORLD CHAMPIONSHIPS 26-27 Season 1優勝記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION 3 優勝記念品</t>
+  </si>
+  <si>
+    <t>ビギナーズバトル2026 SEASON1 参加記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION2 参加記念品</t>
+  </si>
+  <si>
+    <t>ニュータイプチャレンジ 2026 MISSION1 参加記念品</t>
+  </si>
+  <si>
+    <t>新弾構築戦[GD04] 参加・優勝記念品</t>
+  </si>
+  <si>
+    <t>GUNDAM NEXT FUTURE FINAL来場記念品</t>
+  </si>
+  <si>
+    <t>「ガンダムカードゲーム リミテッドBOX Ver.β」交流会</t>
+  </si>
+  <si>
+    <t>『ガンダムカードゲーム スタートガイド』特別付録</t>
+  </si>
+  <si>
+    <t>β版交流会 6月開催分</t>
+  </si>
+  <si>
+    <t>ショップバトル2025 SEASON1 エキスパートショップ 限定参加記念品</t>
+  </si>
+  <si>
+    <t>ガンダムエース 9月号 付録カード</t>
+  </si>
+  <si>
+    <t>店頭配布</t>
+  </si>
+  <si>
+    <t>デモデッキ公式体験会</t>
+  </si>
+  <si>
+    <t>Vジャンプ 9月特大号 付録カード</t>
+  </si>
+  <si>
+    <t>[EVX-01]オフィシャルグッズセット01 FIRST COMBAT</t>
+  </si>
+  <si>
+    <t>ティーチングアプリDLでGETしよう！リソースカードプレゼントキャンペーンVol.2</t>
+  </si>
+  <si>
+    <t>Vジャンプ 3月特大号 付録カード</t>
+  </si>
+  <si>
+    <t>BANDAI CARD GAMES Fest 25-26 in Tokyo 『ガンダムカードゲーム』コンテンツ参加記念品</t>
+  </si>
+  <si>
+    <t>「機動戦士ガンダムSEEDシリーズ」限定戦 参加記念品</t>
+  </si>
+  <si>
+    <t>1st Anniversary リソースカードパック</t>
+  </si>
+  <si>
+    <t>・スタートデッキそのままバトル[ST10] 参加記念品 ・【ST10/EB01】リリースイベント-バトルロワイヤル- 参加記念品</t>
+  </si>
+  <si>
+    <t>「ガンダムカードゲーム リミテッドBOX Ver.β」体験会</t>
+  </si>
+  <si>
+    <t>オフィシャルカードケースセット 01</t>
+  </si>
+  <si>
+    <t>THE GUNDAM BASE POP-UP WORLD TOUR 購入特典</t>
+  </si>
+  <si>
+    <t>FIRST COMBAT 来場記念品</t>
+  </si>
+  <si>
+    <t>BANDAI CARD GAMES Fest 25-26 来場記念品</t>
+  </si>
+  <si>
+    <t>SDガンダム ジージェネレーション エターナル コラボパック</t>
+  </si>
+  <si>
+    <t>『機動戦士ガンダム 鉄血のオルフェンズ ウルズハント -小さな挑戦者の軌跡-』1週目入場者プレゼント</t>
+  </si>
+  <si>
+    <t>ガンダムエース5月号 付録カード</t>
+  </si>
+  <si>
+    <t>BANDAI CARD GAMES Fest 24-25 in Japan(FINAL)</t>
+  </si>
+  <si>
+    <t>BANDAI CARD GAMES Fest　25-26 イベント開催記念商品</t>
+  </si>
+  <si>
+    <t>補充包發售紀念活動 [GD05]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1415,9 +1718,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1720,15 +2024,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="47" customWidth="1"/>
-    <col min="5" max="5" width="60.296875" customWidth="1"/>
+    <col min="4" max="4" width="37.59765625" customWidth="1"/>
+    <col min="5" max="5" width="47" customWidth="1"/>
+    <col min="6" max="6" width="60.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1739,16 +2044,19 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E1" t="s">
         <v>384</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>385</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1759,16 +2067,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1779,16 +2090,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>424</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1799,16 +2113,19 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>425</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1819,16 +2136,19 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>426</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1839,16 +2159,19 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1859,16 +2182,19 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
       </c>
       <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1879,16 +2205,19 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
       </c>
       <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1899,16 +2228,19 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>430</v>
       </c>
       <c r="E9" t="s">
         <v>26</v>
       </c>
       <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1919,16 +2251,19 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1939,16 +2274,19 @@
         <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E11" t="s">
         <v>24</v>
       </c>
       <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1959,16 +2297,19 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>431</v>
       </c>
       <c r="E12" t="s">
         <v>32</v>
       </c>
       <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1979,16 +2320,19 @@
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
       </c>
       <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1999,16 +2343,19 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>433</v>
       </c>
       <c r="E14" t="s">
         <v>38</v>
       </c>
       <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -2019,16 +2366,19 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
       </c>
       <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -2039,16 +2389,19 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
       <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2059,16 +2412,19 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>434</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -2079,16 +2435,19 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>434</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2099,16 +2458,19 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>435</v>
       </c>
       <c r="E19" t="s">
         <v>49</v>
       </c>
       <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -2119,16 +2481,19 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
       <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2139,16 +2504,19 @@
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E21" t="s">
         <v>24</v>
       </c>
       <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -2159,16 +2527,19 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
       </c>
       <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -2179,16 +2550,19 @@
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E23" t="s">
         <v>57</v>
       </c>
       <c r="F23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2199,16 +2573,19 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>438</v>
       </c>
       <c r="E24" t="s">
         <v>60</v>
       </c>
       <c r="F24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2219,16 +2596,19 @@
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>439</v>
       </c>
       <c r="E25" t="s">
         <v>26</v>
       </c>
       <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2239,16 +2619,19 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>438</v>
       </c>
       <c r="E26" t="s">
         <v>60</v>
       </c>
       <c r="F26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -2259,16 +2642,19 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>440</v>
       </c>
       <c r="E27" t="s">
         <v>67</v>
       </c>
       <c r="F27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -2279,16 +2665,19 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>441</v>
       </c>
       <c r="E28" t="s">
         <v>70</v>
       </c>
       <c r="F28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -2299,16 +2688,19 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>442</v>
       </c>
       <c r="E29" t="s">
         <v>73</v>
       </c>
       <c r="F29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -2319,16 +2711,19 @@
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>441</v>
       </c>
       <c r="E30" t="s">
         <v>70</v>
       </c>
       <c r="F30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -2339,16 +2734,19 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>443</v>
       </c>
       <c r="E31" t="s">
         <v>77</v>
       </c>
       <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -2359,16 +2757,19 @@
         <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="E32" t="s">
         <v>79</v>
       </c>
       <c r="F32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -2379,16 +2780,19 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E33" t="s">
         <v>82</v>
       </c>
       <c r="F33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2399,16 +2803,19 @@
         <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E34" t="s">
         <v>84</v>
       </c>
       <c r="F34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -2419,16 +2826,19 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>447</v>
       </c>
       <c r="E35" t="s">
         <v>87</v>
       </c>
       <c r="F35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -2439,16 +2849,19 @@
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>448</v>
       </c>
       <c r="E36" t="s">
         <v>90</v>
       </c>
       <c r="F36" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -2459,16 +2872,19 @@
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>447</v>
       </c>
       <c r="E37" t="s">
         <v>87</v>
       </c>
       <c r="F37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -2479,16 +2895,19 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E38" t="s">
         <v>95</v>
       </c>
       <c r="F38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -2499,16 +2918,19 @@
         <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E39" t="s">
         <v>97</v>
       </c>
       <c r="F39" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -2519,16 +2941,19 @@
         <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>451</v>
       </c>
       <c r="E40" t="s">
         <v>90</v>
       </c>
       <c r="F40" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -2539,16 +2964,19 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E41" t="s">
         <v>95</v>
       </c>
       <c r="F41" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>102</v>
       </c>
@@ -2559,16 +2987,19 @@
         <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
       </c>
       <c r="F42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G42" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>103</v>
       </c>
@@ -2579,16 +3010,19 @@
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>105</v>
+        <v>447</v>
       </c>
       <c r="E43" t="s">
         <v>105</v>
       </c>
       <c r="F43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G43" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>106</v>
       </c>
@@ -2599,16 +3033,19 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>105</v>
+        <v>447</v>
       </c>
       <c r="E44" t="s">
         <v>105</v>
       </c>
       <c r="F44" t="s">
+        <v>105</v>
+      </c>
+      <c r="G44" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>108</v>
       </c>
@@ -2619,16 +3056,19 @@
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>452</v>
       </c>
       <c r="E45" t="s">
         <v>110</v>
       </c>
       <c r="F45" t="s">
+        <v>110</v>
+      </c>
+      <c r="G45" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>111</v>
       </c>
@@ -2639,16 +3079,19 @@
         <v>113</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E46" t="s">
         <v>35</v>
       </c>
       <c r="F46" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>114</v>
       </c>
@@ -2659,16 +3102,19 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>116</v>
+        <v>453</v>
       </c>
       <c r="E47" t="s">
         <v>116</v>
       </c>
       <c r="F47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G47" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -2679,16 +3125,19 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>454</v>
       </c>
       <c r="E48" t="s">
         <v>118</v>
       </c>
       <c r="F48" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>119</v>
       </c>
@@ -2699,16 +3148,19 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E49" t="s">
         <v>21</v>
       </c>
       <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>121</v>
       </c>
@@ -2719,16 +3171,19 @@
         <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
       </c>
       <c r="F50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>122</v>
       </c>
@@ -2739,16 +3194,19 @@
         <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>455</v>
       </c>
       <c r="E51" t="s">
         <v>124</v>
       </c>
       <c r="F51" t="s">
+        <v>124</v>
+      </c>
+      <c r="G51" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>125</v>
       </c>
@@ -2759,16 +3217,19 @@
         <v>127</v>
       </c>
       <c r="D52" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E52" t="s">
         <v>35</v>
       </c>
       <c r="F52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -2779,16 +3240,19 @@
         <v>113</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E53" t="s">
         <v>21</v>
       </c>
       <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>130</v>
       </c>
@@ -2799,16 +3263,19 @@
         <v>131</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E54" t="s">
         <v>24</v>
       </c>
       <c r="F54" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>132</v>
       </c>
@@ -2819,16 +3286,19 @@
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>456</v>
       </c>
       <c r="E55" t="s">
         <v>134</v>
       </c>
       <c r="F55" t="s">
+        <v>134</v>
+      </c>
+      <c r="G55" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>135</v>
       </c>
@@ -2839,16 +3309,19 @@
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="E56" t="s">
         <v>137</v>
       </c>
       <c r="F56" t="s">
+        <v>137</v>
+      </c>
+      <c r="G56" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -2859,16 +3332,19 @@
         <v>127</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E57" t="s">
         <v>21</v>
       </c>
       <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>140</v>
       </c>
@@ -2879,16 +3355,19 @@
         <v>141</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E58" t="s">
         <v>24</v>
       </c>
       <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>142</v>
       </c>
@@ -2899,16 +3378,19 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E59" t="s">
         <v>35</v>
       </c>
       <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>144</v>
       </c>
@@ -2919,16 +3401,19 @@
         <v>127</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E60" t="s">
         <v>21</v>
       </c>
       <c r="F60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>146</v>
       </c>
@@ -2939,16 +3424,19 @@
         <v>141</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E61" t="s">
         <v>24</v>
       </c>
       <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>147</v>
       </c>
@@ -2959,16 +3447,19 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>452</v>
       </c>
       <c r="E62" t="s">
         <v>110</v>
       </c>
       <c r="F62" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>149</v>
       </c>
@@ -2979,16 +3470,19 @@
         <v>127</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E63" t="s">
         <v>21</v>
       </c>
       <c r="F63" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>151</v>
       </c>
@@ -2999,16 +3493,19 @@
         <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="E64" t="s">
         <v>24</v>
       </c>
       <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>152</v>
       </c>
@@ -3019,16 +3516,19 @@
         <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E65" t="s">
         <v>35</v>
       </c>
       <c r="F65" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>154</v>
       </c>
@@ -3039,16 +3539,19 @@
         <v>127</v>
       </c>
       <c r="D66" t="s">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="E66" t="s">
         <v>35</v>
       </c>
       <c r="F66" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>156</v>
       </c>
@@ -3059,16 +3562,19 @@
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>158</v>
+        <v>458</v>
       </c>
       <c r="E67" t="s">
         <v>158</v>
       </c>
       <c r="F67" t="s">
+        <v>158</v>
+      </c>
+      <c r="G67" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -3079,16 +3585,19 @@
         <v>127</v>
       </c>
       <c r="D68" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E68" t="s">
         <v>82</v>
       </c>
       <c r="F68" t="s">
+        <v>82</v>
+      </c>
+      <c r="G68" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>161</v>
       </c>
@@ -3099,16 +3608,19 @@
         <v>141</v>
       </c>
       <c r="D69" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E69" t="s">
         <v>84</v>
       </c>
       <c r="F69" t="s">
+        <v>84</v>
+      </c>
+      <c r="G69" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -3119,16 +3631,19 @@
         <v>127</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E70" t="s">
         <v>55</v>
       </c>
       <c r="F70" t="s">
+        <v>55</v>
+      </c>
+      <c r="G70" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>164</v>
       </c>
@@ -3139,16 +3654,19 @@
         <v>141</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E71" t="s">
         <v>57</v>
       </c>
       <c r="F71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>165</v>
       </c>
@@ -3159,16 +3677,19 @@
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E72" t="s">
         <v>82</v>
       </c>
       <c r="F72" t="s">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>167</v>
       </c>
@@ -3179,16 +3700,19 @@
         <v>23</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E73" t="s">
         <v>84</v>
       </c>
       <c r="F73" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -3199,16 +3723,19 @@
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>459</v>
       </c>
       <c r="E74" t="s">
         <v>169</v>
       </c>
       <c r="F74" t="s">
+        <v>169</v>
+      </c>
+      <c r="G74" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>170</v>
       </c>
@@ -3219,16 +3746,19 @@
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>460</v>
       </c>
       <c r="E75" t="s">
         <v>172</v>
       </c>
       <c r="F75" t="s">
+        <v>172</v>
+      </c>
+      <c r="G75" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>173</v>
       </c>
@@ -3239,16 +3769,19 @@
         <v>127</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E76" t="s">
         <v>55</v>
       </c>
       <c r="F76" t="s">
+        <v>55</v>
+      </c>
+      <c r="G76" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>175</v>
       </c>
@@ -3259,16 +3792,19 @@
         <v>141</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E77" t="s">
         <v>57</v>
       </c>
       <c r="F77" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>176</v>
       </c>
@@ -3279,16 +3815,19 @@
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E78" t="s">
         <v>82</v>
       </c>
       <c r="F78" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>178</v>
       </c>
@@ -3299,16 +3838,19 @@
         <v>23</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E79" t="s">
         <v>84</v>
       </c>
       <c r="F79" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>179</v>
       </c>
@@ -3319,16 +3861,19 @@
         <v>127</v>
       </c>
       <c r="D80" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E80" t="s">
         <v>82</v>
       </c>
       <c r="F80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>181</v>
       </c>
@@ -3339,16 +3884,19 @@
         <v>141</v>
       </c>
       <c r="D81" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E81" t="s">
         <v>84</v>
       </c>
       <c r="F81" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>182</v>
       </c>
@@ -3359,16 +3907,19 @@
         <v>127</v>
       </c>
       <c r="D82" t="s">
-        <v>184</v>
+        <v>461</v>
       </c>
       <c r="E82" t="s">
         <v>184</v>
       </c>
       <c r="F82" t="s">
+        <v>184</v>
+      </c>
+      <c r="G82" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>185</v>
       </c>
@@ -3379,16 +3930,19 @@
         <v>5</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
+        <v>462</v>
       </c>
       <c r="E83" t="s">
         <v>187</v>
       </c>
       <c r="F83" t="s">
+        <v>187</v>
+      </c>
+      <c r="G83" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>188</v>
       </c>
@@ -3399,16 +3953,19 @@
         <v>127</v>
       </c>
       <c r="D84" t="s">
-        <v>169</v>
+        <v>459</v>
       </c>
       <c r="E84" t="s">
         <v>169</v>
       </c>
       <c r="F84" t="s">
+        <v>169</v>
+      </c>
+      <c r="G84" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>190</v>
       </c>
@@ -3419,16 +3976,19 @@
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E85" t="s">
         <v>55</v>
       </c>
       <c r="F85" t="s">
+        <v>55</v>
+      </c>
+      <c r="G85" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>192</v>
       </c>
@@ -3439,16 +3999,19 @@
         <v>23</v>
       </c>
       <c r="D86" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E86" t="s">
         <v>57</v>
       </c>
       <c r="F86" t="s">
+        <v>57</v>
+      </c>
+      <c r="G86" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>193</v>
       </c>
@@ -3459,16 +4022,19 @@
         <v>127</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>463</v>
       </c>
       <c r="E87" t="s">
         <v>26</v>
       </c>
       <c r="F87" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>195</v>
       </c>
@@ -3479,16 +4045,19 @@
         <v>127</v>
       </c>
       <c r="D88" t="s">
-        <v>172</v>
+        <v>464</v>
       </c>
       <c r="E88" t="s">
         <v>172</v>
       </c>
       <c r="F88" t="s">
+        <v>172</v>
+      </c>
+      <c r="G88" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -3499,16 +4068,19 @@
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E89" t="s">
         <v>55</v>
       </c>
       <c r="F89" t="s">
+        <v>55</v>
+      </c>
+      <c r="G89" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -3519,16 +4091,19 @@
         <v>23</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E90" t="s">
         <v>57</v>
       </c>
       <c r="F90" t="s">
+        <v>57</v>
+      </c>
+      <c r="G90" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>199</v>
       </c>
@@ -3539,16 +4114,19 @@
         <v>127</v>
       </c>
       <c r="D91" t="s">
-        <v>187</v>
+        <v>462</v>
       </c>
       <c r="E91" t="s">
         <v>187</v>
       </c>
       <c r="F91" t="s">
+        <v>187</v>
+      </c>
+      <c r="G91" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -3559,16 +4137,19 @@
         <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E92" t="s">
         <v>82</v>
       </c>
       <c r="F92" t="s">
+        <v>82</v>
+      </c>
+      <c r="G92" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>203</v>
       </c>
@@ -3579,16 +4160,19 @@
         <v>131</v>
       </c>
       <c r="D93" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E93" t="s">
         <v>84</v>
       </c>
       <c r="F93" t="s">
+        <v>84</v>
+      </c>
+      <c r="G93" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>204</v>
       </c>
@@ -3599,16 +4183,19 @@
         <v>113</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E94" t="s">
         <v>55</v>
       </c>
       <c r="F94" t="s">
+        <v>55</v>
+      </c>
+      <c r="G94" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>206</v>
       </c>
@@ -3619,16 +4206,19 @@
         <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E95" t="s">
         <v>57</v>
       </c>
       <c r="F95" t="s">
+        <v>57</v>
+      </c>
+      <c r="G95" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>207</v>
       </c>
@@ -3639,16 +4229,19 @@
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E96" t="s">
         <v>82</v>
       </c>
       <c r="F96" t="s">
+        <v>82</v>
+      </c>
+      <c r="G96" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>209</v>
       </c>
@@ -3659,16 +4252,19 @@
         <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E97" t="s">
         <v>84</v>
       </c>
       <c r="F97" t="s">
+        <v>84</v>
+      </c>
+      <c r="G97" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>210</v>
       </c>
@@ -3679,16 +4275,19 @@
         <v>127</v>
       </c>
       <c r="D98" t="s">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="E98" t="s">
         <v>172</v>
       </c>
       <c r="F98" t="s">
+        <v>172</v>
+      </c>
+      <c r="G98" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>212</v>
       </c>
@@ -3699,16 +4298,19 @@
         <v>127</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E99" t="s">
         <v>82</v>
       </c>
       <c r="F99" t="s">
+        <v>82</v>
+      </c>
+      <c r="G99" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>214</v>
       </c>
@@ -3719,16 +4321,19 @@
         <v>141</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="E100" t="s">
         <v>84</v>
       </c>
       <c r="F100" t="s">
+        <v>84</v>
+      </c>
+      <c r="G100" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>215</v>
       </c>
@@ -3739,16 +4344,19 @@
         <v>127</v>
       </c>
       <c r="D101" t="s">
-        <v>187</v>
+        <v>462</v>
       </c>
       <c r="E101" t="s">
         <v>187</v>
       </c>
       <c r="F101" t="s">
+        <v>187</v>
+      </c>
+      <c r="G101" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>217</v>
       </c>
@@ -3759,16 +4367,19 @@
         <v>113</v>
       </c>
       <c r="D102" t="s">
-        <v>95</v>
+        <v>466</v>
       </c>
       <c r="E102" t="s">
         <v>95</v>
       </c>
       <c r="F102" t="s">
+        <v>95</v>
+      </c>
+      <c r="G102" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>219</v>
       </c>
@@ -3779,16 +4390,19 @@
         <v>131</v>
       </c>
       <c r="D103" t="s">
-        <v>97</v>
+        <v>467</v>
       </c>
       <c r="E103" t="s">
         <v>97</v>
       </c>
       <c r="F103" t="s">
+        <v>97</v>
+      </c>
+      <c r="G103" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>220</v>
       </c>
@@ -3799,16 +4413,19 @@
         <v>127</v>
       </c>
       <c r="D104" t="s">
-        <v>222</v>
+        <v>468</v>
       </c>
       <c r="E104" t="s">
         <v>222</v>
       </c>
       <c r="F104" t="s">
+        <v>222</v>
+      </c>
+      <c r="G104" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>223</v>
       </c>
@@ -3819,16 +4436,19 @@
         <v>127</v>
       </c>
       <c r="D105" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E105" t="s">
         <v>95</v>
       </c>
       <c r="F105" t="s">
+        <v>95</v>
+      </c>
+      <c r="G105" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -3839,16 +4459,19 @@
         <v>141</v>
       </c>
       <c r="D106" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E106" t="s">
         <v>97</v>
       </c>
       <c r="F106" t="s">
+        <v>97</v>
+      </c>
+      <c r="G106" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3859,16 +4482,19 @@
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>118</v>
+        <v>454</v>
       </c>
       <c r="E107" t="s">
         <v>118</v>
       </c>
       <c r="F107" t="s">
+        <v>118</v>
+      </c>
+      <c r="G107" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>228</v>
       </c>
@@ -3879,16 +4505,19 @@
         <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>230</v>
+        <v>469</v>
       </c>
       <c r="E108" t="s">
         <v>230</v>
       </c>
       <c r="F108" t="s">
+        <v>230</v>
+      </c>
+      <c r="G108" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>231</v>
       </c>
@@ -3899,16 +4528,19 @@
         <v>5</v>
       </c>
       <c r="D109" t="s">
-        <v>233</v>
+        <v>470</v>
       </c>
       <c r="E109" t="s">
         <v>233</v>
       </c>
       <c r="F109" t="s">
+        <v>233</v>
+      </c>
+      <c r="G109" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>234</v>
       </c>
@@ -3919,16 +4551,19 @@
         <v>127</v>
       </c>
       <c r="D110" t="s">
-        <v>118</v>
+        <v>454</v>
       </c>
       <c r="E110" t="s">
         <v>118</v>
       </c>
       <c r="F110" t="s">
+        <v>118</v>
+      </c>
+      <c r="G110" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>236</v>
       </c>
@@ -3939,16 +4574,19 @@
         <v>127</v>
       </c>
       <c r="D111" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E111" t="s">
         <v>95</v>
       </c>
       <c r="F111" t="s">
+        <v>95</v>
+      </c>
+      <c r="G111" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>238</v>
       </c>
@@ -3959,16 +4597,19 @@
         <v>141</v>
       </c>
       <c r="D112" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E112" t="s">
         <v>97</v>
       </c>
       <c r="F112" t="s">
+        <v>97</v>
+      </c>
+      <c r="G112" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>239</v>
       </c>
@@ -3979,16 +4620,19 @@
         <v>113</v>
       </c>
       <c r="D113" t="s">
-        <v>241</v>
+        <v>471</v>
       </c>
       <c r="E113" t="s">
         <v>241</v>
       </c>
       <c r="F113" t="s">
+        <v>241</v>
+      </c>
+      <c r="G113" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -3999,16 +4643,19 @@
         <v>13</v>
       </c>
       <c r="D114" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E114" t="s">
         <v>95</v>
       </c>
       <c r="F114" t="s">
+        <v>95</v>
+      </c>
+      <c r="G114" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>244</v>
       </c>
@@ -4019,16 +4666,19 @@
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E115" t="s">
         <v>97</v>
       </c>
       <c r="F115" t="s">
+        <v>97</v>
+      </c>
+      <c r="G115" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>245</v>
       </c>
@@ -4039,16 +4689,19 @@
         <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E116" t="s">
         <v>55</v>
       </c>
       <c r="F116" t="s">
+        <v>55</v>
+      </c>
+      <c r="G116" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>247</v>
       </c>
@@ -4059,16 +4712,19 @@
         <v>23</v>
       </c>
       <c r="D117" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E117" t="s">
         <v>57</v>
       </c>
       <c r="F117" t="s">
+        <v>57</v>
+      </c>
+      <c r="G117" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>248</v>
       </c>
@@ -4079,16 +4735,19 @@
         <v>113</v>
       </c>
       <c r="D118" t="s">
-        <v>222</v>
+        <v>468</v>
       </c>
       <c r="E118" t="s">
         <v>222</v>
       </c>
       <c r="F118" t="s">
+        <v>222</v>
+      </c>
+      <c r="G118" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>250</v>
       </c>
@@ -4099,16 +4758,19 @@
         <v>113</v>
       </c>
       <c r="D119" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E119" t="s">
         <v>95</v>
       </c>
       <c r="F119" t="s">
+        <v>95</v>
+      </c>
+      <c r="G119" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -4119,16 +4781,19 @@
         <v>131</v>
       </c>
       <c r="D120" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E120" t="s">
         <v>97</v>
       </c>
       <c r="F120" t="s">
+        <v>97</v>
+      </c>
+      <c r="G120" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>253</v>
       </c>
@@ -4139,16 +4804,19 @@
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>118</v>
+        <v>454</v>
       </c>
       <c r="E121" t="s">
         <v>118</v>
       </c>
       <c r="F121" t="s">
+        <v>118</v>
+      </c>
+      <c r="G121" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>255</v>
       </c>
@@ -4159,16 +4827,19 @@
         <v>127</v>
       </c>
       <c r="D122" t="s">
-        <v>118</v>
+        <v>454</v>
       </c>
       <c r="E122" t="s">
         <v>118</v>
       </c>
       <c r="F122" t="s">
+        <v>118</v>
+      </c>
+      <c r="G122" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>257</v>
       </c>
@@ -4179,16 +4850,19 @@
         <v>13</v>
       </c>
       <c r="D123" t="s">
-        <v>55</v>
+        <v>436</v>
       </c>
       <c r="E123" t="s">
         <v>55</v>
       </c>
       <c r="F123" t="s">
+        <v>55</v>
+      </c>
+      <c r="G123" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>259</v>
       </c>
@@ -4199,16 +4873,19 @@
         <v>23</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="E124" t="s">
         <v>57</v>
       </c>
       <c r="F124" t="s">
+        <v>57</v>
+      </c>
+      <c r="G124" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>260</v>
       </c>
@@ -4219,16 +4896,19 @@
         <v>127</v>
       </c>
       <c r="D125" t="s">
-        <v>90</v>
+        <v>472</v>
       </c>
       <c r="E125" t="s">
         <v>90</v>
       </c>
       <c r="F125" t="s">
+        <v>90</v>
+      </c>
+      <c r="G125" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>262</v>
       </c>
@@ -4239,16 +4919,19 @@
         <v>127</v>
       </c>
       <c r="D126" t="s">
-        <v>95</v>
+        <v>449</v>
       </c>
       <c r="E126" t="s">
         <v>95</v>
       </c>
       <c r="F126" t="s">
+        <v>95</v>
+      </c>
+      <c r="G126" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>264</v>
       </c>
@@ -4259,16 +4942,19 @@
         <v>141</v>
       </c>
       <c r="D127" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="E127" t="s">
         <v>97</v>
       </c>
       <c r="F127" t="s">
+        <v>97</v>
+      </c>
+      <c r="G127" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>265</v>
       </c>
@@ -4279,16 +4965,19 @@
         <v>127</v>
       </c>
       <c r="D128" t="s">
-        <v>266</v>
+        <v>473</v>
       </c>
       <c r="E128" t="s">
         <v>266</v>
       </c>
       <c r="F128" t="s">
+        <v>266</v>
+      </c>
+      <c r="G128" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -4299,16 +4988,19 @@
         <v>113</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>474</v>
       </c>
       <c r="E129" t="s">
         <v>269</v>
       </c>
       <c r="F129" t="s">
+        <v>269</v>
+      </c>
+      <c r="G129" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>270</v>
       </c>
@@ -4319,16 +5011,19 @@
         <v>127</v>
       </c>
       <c r="D130" t="s">
-        <v>269</v>
+        <v>474</v>
       </c>
       <c r="E130" t="s">
         <v>269</v>
       </c>
       <c r="F130" t="s">
+        <v>269</v>
+      </c>
+      <c r="G130" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>272</v>
       </c>
@@ -4339,16 +5034,19 @@
         <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>274</v>
+        <v>475</v>
       </c>
       <c r="E131" t="s">
         <v>274</v>
       </c>
       <c r="F131" t="s">
+        <v>274</v>
+      </c>
+      <c r="G131" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>275</v>
       </c>
@@ -4359,16 +5057,19 @@
         <v>17</v>
       </c>
       <c r="D132" t="s">
+        <v>476</v>
+      </c>
+      <c r="E132" t="s">
         <v>277</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>386</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>278</v>
       </c>
@@ -4379,16 +5080,19 @@
         <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>280</v>
+        <v>477</v>
       </c>
       <c r="E133" t="s">
         <v>280</v>
       </c>
       <c r="F133" t="s">
+        <v>280</v>
+      </c>
+      <c r="G133" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>281</v>
       </c>
@@ -4399,16 +5103,19 @@
         <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>283</v>
+        <v>478</v>
       </c>
       <c r="E134" t="s">
         <v>283</v>
       </c>
       <c r="F134" t="s">
+        <v>283</v>
+      </c>
+      <c r="G134" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>284</v>
       </c>
@@ -4419,16 +5126,19 @@
         <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>280</v>
+        <v>479</v>
       </c>
       <c r="E135" t="s">
         <v>280</v>
       </c>
       <c r="F135" t="s">
+        <v>280</v>
+      </c>
+      <c r="G135" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>286</v>
       </c>
@@ -4439,16 +5149,19 @@
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="E136" t="s">
         <v>280</v>
       </c>
       <c r="F136" t="s">
+        <v>280</v>
+      </c>
+      <c r="G136" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>288</v>
       </c>
@@ -4459,16 +5172,19 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>280</v>
+        <v>481</v>
       </c>
       <c r="E137" t="s">
         <v>280</v>
       </c>
       <c r="F137" t="s">
+        <v>280</v>
+      </c>
+      <c r="G137" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>290</v>
       </c>
@@ -4479,16 +5195,19 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
+        <v>482</v>
+      </c>
+      <c r="E138" t="s">
         <v>277</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>386</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>292</v>
       </c>
@@ -4499,16 +5218,19 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>280</v>
+        <v>483</v>
       </c>
       <c r="E139" t="s">
         <v>280</v>
       </c>
       <c r="F139" t="s">
+        <v>280</v>
+      </c>
+      <c r="G139" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>294</v>
       </c>
@@ -4519,16 +5241,19 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>296</v>
+        <v>481</v>
       </c>
       <c r="E140" t="s">
         <v>296</v>
       </c>
       <c r="F140" t="s">
+        <v>296</v>
+      </c>
+      <c r="G140" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>297</v>
       </c>
@@ -4539,16 +5264,19 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E141" t="s">
         <v>299</v>
       </c>
       <c r="F141" t="s">
+        <v>299</v>
+      </c>
+      <c r="G141" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>300</v>
       </c>
@@ -4559,16 +5287,19 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E142" t="s">
         <v>299</v>
       </c>
       <c r="F142" t="s">
+        <v>299</v>
+      </c>
+      <c r="G142" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>302</v>
       </c>
@@ -4579,16 +5310,19 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E143" t="s">
         <v>299</v>
       </c>
       <c r="F143" t="s">
+        <v>299</v>
+      </c>
+      <c r="G143" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>304</v>
       </c>
@@ -4599,16 +5333,19 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E144" t="s">
         <v>299</v>
       </c>
       <c r="F144" t="s">
+        <v>299</v>
+      </c>
+      <c r="G144" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>306</v>
       </c>
@@ -4619,16 +5356,19 @@
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E145" t="s">
         <v>299</v>
       </c>
       <c r="F145" t="s">
+        <v>299</v>
+      </c>
+      <c r="G145" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>308</v>
       </c>
@@ -4639,16 +5379,19 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E146" t="s">
         <v>299</v>
       </c>
       <c r="F146" t="s">
+        <v>299</v>
+      </c>
+      <c r="G146" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>310</v>
       </c>
@@ -4659,16 +5402,19 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E147" t="s">
         <v>299</v>
       </c>
       <c r="F147" t="s">
+        <v>299</v>
+      </c>
+      <c r="G147" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>312</v>
       </c>
@@ -4679,16 +5425,19 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E148" t="s">
         <v>299</v>
       </c>
       <c r="F148" t="s">
+        <v>299</v>
+      </c>
+      <c r="G148" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>314</v>
       </c>
@@ -4699,16 +5448,19 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E149" t="s">
         <v>299</v>
       </c>
       <c r="F149" t="s">
+        <v>299</v>
+      </c>
+      <c r="G149" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>316</v>
       </c>
@@ -4719,16 +5471,19 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="E150" t="s">
         <v>299</v>
       </c>
       <c r="F150" t="s">
+        <v>299</v>
+      </c>
+      <c r="G150" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>318</v>
       </c>
@@ -4739,16 +5494,19 @@
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>105</v>
+        <v>485</v>
       </c>
       <c r="E151" t="s">
         <v>105</v>
       </c>
       <c r="F151" t="s">
+        <v>105</v>
+      </c>
+      <c r="G151" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>320</v>
       </c>
@@ -4759,16 +5517,19 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>26</v>
+        <v>486</v>
       </c>
       <c r="E152" t="s">
         <v>26</v>
       </c>
       <c r="F152" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>322</v>
       </c>
@@ -4779,16 +5540,19 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>26</v>
+        <v>487</v>
       </c>
       <c r="E153" t="s">
         <v>26</v>
       </c>
       <c r="F153" t="s">
+        <v>26</v>
+      </c>
+      <c r="G153" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>324</v>
       </c>
@@ -4799,16 +5563,19 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>326</v>
+        <v>488</v>
       </c>
       <c r="E154" t="s">
         <v>326</v>
       </c>
       <c r="F154" t="s">
+        <v>326</v>
+      </c>
+      <c r="G154" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>327</v>
       </c>
@@ -4819,16 +5586,19 @@
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E155" t="s">
         <v>329</v>
       </c>
       <c r="F155" t="s">
+        <v>329</v>
+      </c>
+      <c r="G155" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>330</v>
       </c>
@@ -4839,16 +5609,19 @@
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E156" t="s">
         <v>329</v>
       </c>
       <c r="F156" t="s">
+        <v>329</v>
+      </c>
+      <c r="G156" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>332</v>
       </c>
@@ -4859,16 +5632,19 @@
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E157" t="s">
         <v>329</v>
       </c>
       <c r="F157" t="s">
+        <v>329</v>
+      </c>
+      <c r="G157" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>334</v>
       </c>
@@ -4879,16 +5655,19 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E158" t="s">
         <v>329</v>
       </c>
       <c r="F158" t="s">
+        <v>329</v>
+      </c>
+      <c r="G158" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+    <row r="159" spans="1:7" ht="85.5" x14ac:dyDescent="5.0999999999999996">
       <c r="A159" t="s">
         <v>336</v>
       </c>
@@ -4899,16 +5678,19 @@
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E159" t="s">
         <v>329</v>
       </c>
-      <c r="F159" s="1" t="s">
+      <c r="F159" t="s">
+        <v>329</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>338</v>
       </c>
@@ -4919,16 +5701,19 @@
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E160" t="s">
         <v>329</v>
       </c>
       <c r="F160" t="s">
+        <v>329</v>
+      </c>
+      <c r="G160" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>340</v>
       </c>
@@ -4939,16 +5724,19 @@
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E161" t="s">
         <v>329</v>
       </c>
       <c r="F161" t="s">
+        <v>329</v>
+      </c>
+      <c r="G161" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>342</v>
       </c>
@@ -4959,16 +5747,19 @@
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="E162" t="s">
         <v>329</v>
       </c>
       <c r="F162" t="s">
+        <v>329</v>
+      </c>
+      <c r="G162" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>344</v>
       </c>
@@ -4979,16 +5770,19 @@
         <v>17</v>
       </c>
       <c r="D163" t="s">
-        <v>26</v>
+        <v>490</v>
       </c>
       <c r="E163" t="s">
         <v>26</v>
       </c>
       <c r="F163" t="s">
+        <v>26</v>
+      </c>
+      <c r="G163" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>346</v>
       </c>
@@ -4999,16 +5793,19 @@
         <v>17</v>
       </c>
       <c r="D164" t="s">
+        <v>491</v>
+      </c>
+      <c r="E164" t="s">
         <v>348</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>387</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>349</v>
       </c>
@@ -5019,16 +5816,19 @@
         <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>351</v>
+        <v>492</v>
       </c>
       <c r="E165" t="s">
         <v>351</v>
       </c>
       <c r="F165" t="s">
+        <v>351</v>
+      </c>
+      <c r="G165" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>352</v>
       </c>
@@ -5039,16 +5839,19 @@
         <v>17</v>
       </c>
       <c r="D166" t="s">
-        <v>354</v>
+        <v>493</v>
       </c>
       <c r="E166" t="s">
         <v>354</v>
       </c>
       <c r="F166" t="s">
+        <v>354</v>
+      </c>
+      <c r="G166" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>355</v>
       </c>
@@ -5059,16 +5862,19 @@
         <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>357</v>
+        <v>494</v>
       </c>
       <c r="E167" t="s">
         <v>357</v>
       </c>
       <c r="F167" t="s">
+        <v>357</v>
+      </c>
+      <c r="G167" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>358</v>
       </c>
@@ -5079,16 +5885,19 @@
         <v>17</v>
       </c>
       <c r="D168" t="s">
-        <v>360</v>
+        <v>495</v>
       </c>
       <c r="E168" t="s">
         <v>360</v>
       </c>
       <c r="F168" t="s">
+        <v>360</v>
+      </c>
+      <c r="G168" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>361</v>
       </c>
@@ -5099,16 +5908,19 @@
         <v>17</v>
       </c>
       <c r="D169" t="s">
+        <v>496</v>
+      </c>
+      <c r="E169" t="s">
         <v>363</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>388</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>364</v>
       </c>
@@ -5119,16 +5931,19 @@
         <v>17</v>
       </c>
       <c r="D170" t="s">
+        <v>496</v>
+      </c>
+      <c r="E170" t="s">
         <v>363</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>388</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>366</v>
       </c>
@@ -5139,16 +5954,19 @@
         <v>17</v>
       </c>
       <c r="D171" t="s">
+        <v>496</v>
+      </c>
+      <c r="E171" t="s">
         <v>363</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>388</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>368</v>
       </c>
@@ -5159,16 +5977,19 @@
         <v>17</v>
       </c>
       <c r="D172" t="s">
+        <v>496</v>
+      </c>
+      <c r="E172" t="s">
         <v>363</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>388</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>370</v>
       </c>
@@ -5179,16 +6000,19 @@
         <v>17</v>
       </c>
       <c r="D173" t="s">
+        <v>496</v>
+      </c>
+      <c r="E173" t="s">
         <v>363</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>388</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>372</v>
       </c>
@@ -5199,16 +6023,19 @@
         <v>17</v>
       </c>
       <c r="D174" t="s">
-        <v>26</v>
+        <v>497</v>
       </c>
       <c r="E174" t="s">
         <v>26</v>
       </c>
       <c r="F174" t="s">
+        <v>26</v>
+      </c>
+      <c r="G174" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>374</v>
       </c>
@@ -5219,16 +6046,19 @@
         <v>17</v>
       </c>
       <c r="D175" t="s">
-        <v>26</v>
+        <v>498</v>
       </c>
       <c r="E175" t="s">
         <v>26</v>
       </c>
       <c r="F175" t="s">
+        <v>26</v>
+      </c>
+      <c r="G175" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>376</v>
       </c>
@@ -5239,16 +6069,19 @@
         <v>17</v>
       </c>
       <c r="D176" t="s">
-        <v>378</v>
+        <v>499</v>
       </c>
       <c r="E176" t="s">
         <v>378</v>
       </c>
       <c r="F176" t="s">
+        <v>378</v>
+      </c>
+      <c r="G176" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>379</v>
       </c>
@@ -5259,16 +6092,19 @@
         <v>17</v>
       </c>
       <c r="D177" t="s">
-        <v>351</v>
+        <v>492</v>
       </c>
       <c r="E177" t="s">
         <v>351</v>
       </c>
       <c r="F177" t="s">
+        <v>351</v>
+      </c>
+      <c r="G177" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>381</v>
       </c>
@@ -5279,13 +6115,85 @@
         <v>17</v>
       </c>
       <c r="D178" t="s">
+        <v>500</v>
+      </c>
+      <c r="E178" t="s">
         <v>383</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>389</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" t="s">
+        <v>411</v>
+      </c>
+      <c r="B179" t="s">
+        <v>418</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D179" t="s">
+        <v>422</v>
+      </c>
+      <c r="E179" t="s">
+        <v>26</v>
+      </c>
+      <c r="F179" t="s">
+        <v>26</v>
+      </c>
+      <c r="G179" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" t="s">
+        <v>412</v>
+      </c>
+      <c r="B180" t="s">
+        <v>414</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D180" t="s">
+        <v>421</v>
+      </c>
+      <c r="E180" t="s">
+        <v>501</v>
+      </c>
+      <c r="F180" t="s">
+        <v>501</v>
+      </c>
+      <c r="G180" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" t="s">
+        <v>413</v>
+      </c>
+      <c r="B181" t="s">
+        <v>415</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D181" t="s">
+        <v>421</v>
+      </c>
+      <c r="E181" t="s">
+        <v>501</v>
+      </c>
+      <c r="F181" t="s">
+        <v>501</v>
+      </c>
+      <c r="G181" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
